--- a/Data/EXCEL/Transfer/salemon/202208/9958-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/9958-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CA2EFAC-EF7C-4082-8F01-D495DE1B8C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCBF103F-C73E-48ED-847A-2DC06A556F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="9958-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,18 +1227,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q240"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.125" customWidth="1"/>
-    <col min="2" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="9.5" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="16" width="9.5" customWidth="1"/>
-    <col min="17" max="17" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="5" width="13.875" customWidth="1"/>
+    <col min="6" max="7" width="15.25" customWidth="1"/>
+    <col min="8" max="8" width="13.875" customWidth="1"/>
+    <col min="9" max="9" width="15.875" customWidth="1"/>
+    <col min="10" max="16" width="13.875" customWidth="1"/>
+    <col min="17" max="17" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1265,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1296,7 +1304,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1339,7 +1347,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1378,7 +1386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1431,7 +1439,7 @@
         <v>-13.2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1484,7 +1492,7 @@
         <v>-9.86</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1537,7 +1545,7 @@
         <v>-1.75</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1590,7 +1598,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1643,7 +1651,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1696,7 +1704,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1749,7 +1757,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1802,7 +1810,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1855,7 +1863,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1908,7 +1916,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1961,7 +1969,7 @@
         <v>61.3</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2014,7 +2022,7 @@
         <v>63.4</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2067,7 +2075,7 @@
         <v>59.1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2120,7 +2128,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2173,7 +2181,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2226,7 +2234,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2279,7 +2287,7 @@
         <v>46.2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2332,7 +2340,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2385,7 +2393,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2438,7 +2446,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2491,7 +2499,7 @@
         <v>166.8</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2544,7 +2552,7 @@
         <v>192.2</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2597,7 +2605,7 @@
         <v>204.4</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2650,7 +2658,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2703,7 +2711,7 @@
         <v>217.7</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2756,7 +2764,7 @@
         <v>210.7</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2809,7 +2817,7 @@
         <v>190.2</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2862,7 +2870,7 @@
         <v>179.4</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2915,7 +2923,7 @@
         <v>191.4</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2968,7 +2976,7 @@
         <v>195.1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3021,7 +3029,7 @@
         <v>260.3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3074,7 +3082,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3127,7 +3135,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3180,7 +3188,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3233,7 +3241,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3286,7 +3294,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3339,7 +3347,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3392,7 +3400,7 @@
         <v>9.36</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3445,7 +3453,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3498,7 +3506,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3551,7 +3559,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3604,7 +3612,7 @@
         <v>-2.89</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3657,7 +3665,7 @@
         <v>-2.87</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3710,7 +3718,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3763,7 +3771,7 @@
         <v>-19.3</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3816,7 +3824,7 @@
         <v>-19.8</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3869,7 +3877,7 @@
         <v>-21.2</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3922,7 +3930,7 @@
         <v>-19.8</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3975,7 +3983,7 @@
         <v>-22.1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4028,7 +4036,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4081,7 +4089,7 @@
         <v>-26.5</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4134,7 +4142,7 @@
         <v>-26.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4187,7 +4195,7 @@
         <v>-23.4</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4240,7 +4248,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4293,7 +4301,7 @@
         <v>-25.1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4346,7 +4354,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4399,7 +4407,7 @@
         <v>-10.199999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4452,7 +4460,7 @@
         <v>-9.7200000000000006</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4505,7 +4513,7 @@
         <v>-9.5399999999999991</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4558,7 +4566,7 @@
         <v>-9.65</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4611,7 +4619,7 @@
         <v>-7.62</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4664,7 +4672,7 @@
         <v>-7.8</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4717,7 +4725,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4770,7 +4778,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4823,7 +4831,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4876,7 +4884,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4929,7 +4937,7 @@
         <v>-17.3</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4982,7 +4990,7 @@
         <v>-35.700000000000003</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5035,7 +5043,7 @@
         <v>-24.6</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5088,7 +5096,7 @@
         <v>-24.5</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5141,7 +5149,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5194,7 +5202,7 @@
         <v>-18.3</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5247,7 +5255,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5300,7 +5308,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5353,7 +5361,7 @@
         <v>-8.2799999999999994</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5406,7 +5414,7 @@
         <v>-7.77</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5459,7 +5467,7 @@
         <v>-8.23</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5512,7 +5520,7 @@
         <v>-14.1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5565,7 +5573,7 @@
         <v>-11.9</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5618,7 +5626,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5671,7 +5679,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5724,7 +5732,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5777,7 +5785,7 @@
         <v>-0.65</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5830,7 +5838,7 @@
         <v>-4.24</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5883,7 +5891,7 @@
         <v>-5.58</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5936,7 +5944,7 @@
         <v>-8.57</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5989,7 +5997,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6042,7 +6050,7 @@
         <v>-3.21</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6095,7 +6103,7 @@
         <v>-3.71</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6148,7 +6156,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6201,7 +6209,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6254,7 +6262,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6307,7 +6315,7 @@
         <v>-16.8</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6360,7 +6368,7 @@
         <v>-16.3</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6413,7 +6421,7 @@
         <v>-16.8</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6466,7 +6474,7 @@
         <v>-16.399999999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6519,7 +6527,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6572,7 +6580,7 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6625,7 +6633,7 @@
         <v>-9.17</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6678,7 +6686,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6731,7 +6739,7 @@
         <v>-7.85</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6784,7 +6792,7 @@
         <v>-10.9</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6837,7 +6845,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6890,7 +6898,7 @@
         <v>-16.899999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6943,7 +6951,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6996,7 +7004,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7049,7 +7057,7 @@
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7102,7 +7110,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7155,7 +7163,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7208,7 +7216,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7261,7 +7269,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7314,7 +7322,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7367,7 +7375,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7420,7 +7428,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7473,7 +7481,7 @@
         <v>-2.93</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7526,7 +7534,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7579,7 +7587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7632,7 +7640,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7685,7 +7693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7738,7 +7746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7791,7 +7799,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7844,7 +7852,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7897,7 +7905,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7950,7 +7958,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8003,7 +8011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8056,7 +8064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8109,7 +8117,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8162,7 +8170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8215,7 +8223,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8268,7 +8276,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8321,7 +8329,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8374,7 +8382,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8427,7 +8435,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8480,7 +8488,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8533,7 +8541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8586,7 +8594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8639,7 +8647,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8692,7 +8700,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8745,7 +8753,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8798,7 +8806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8851,7 +8859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8904,7 +8912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8957,7 +8965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9010,7 +9018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9063,7 +9071,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9116,7 +9124,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9169,7 +9177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9222,7 +9230,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9275,7 +9283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9328,7 +9336,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9381,7 +9389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9434,7 +9442,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9487,7 +9495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9540,7 +9548,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9593,7 +9601,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9646,7 +9654,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9699,7 +9707,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9752,7 +9760,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9805,7 +9813,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9858,7 +9866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9911,7 +9919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9964,7 +9972,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10017,7 +10025,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10070,7 +10078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10123,7 +10131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10176,7 +10184,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10229,7 +10237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10282,7 +10290,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10335,7 +10343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10388,7 +10396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10441,7 +10449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10494,7 +10502,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10547,7 +10555,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10600,7 +10608,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10653,7 +10661,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10706,7 +10714,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10759,7 +10767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10812,7 +10820,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10865,7 +10873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10918,7 +10926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10971,7 +10979,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11024,7 +11032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11077,7 +11085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11130,7 +11138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11183,7 +11191,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11236,7 +11244,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11289,7 +11297,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11342,7 +11350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11395,7 +11403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11448,7 +11456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11501,7 +11509,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11554,7 +11562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11607,7 +11615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11660,7 +11668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11713,7 +11721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11766,7 +11774,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11819,7 +11827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11872,7 +11880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11925,7 +11933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11978,7 +11986,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12031,7 +12039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12084,7 +12092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12137,7 +12145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12190,7 +12198,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12243,7 +12251,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12296,7 +12304,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12349,7 +12357,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12402,7 +12410,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12455,7 +12463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12508,7 +12516,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12561,7 +12569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12614,7 +12622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12667,7 +12675,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12720,7 +12728,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12773,7 +12781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12826,7 +12834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12879,7 +12887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12932,7 +12940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12985,7 +12993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13038,7 +13046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13091,7 +13099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13144,7 +13152,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13197,7 +13205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13250,7 +13258,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13303,7 +13311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13356,7 +13364,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13409,7 +13417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13462,7 +13470,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13515,7 +13523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13568,7 +13576,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13621,7 +13629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13674,7 +13682,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13727,7 +13735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13780,7 +13788,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13833,7 +13841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13901,7 +13909,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>